--- a/diseases/d059/2005-2009.xlsx
+++ b/diseases/d059/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1901,9 +1892,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2185,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2493,9 +2478,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2771,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3085,9 +3064,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3381,9 +3357,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3677,9 +3650,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3973,9 +3943,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4269,9 +4236,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4565,9 +4529,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4822,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5215,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5553,9 +5508,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5849,9 +5801,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -6145,9 +6094,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6441,9 +6387,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6737,9 +6680,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7033,9 +6973,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7329,9 +7266,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -7625,9 +7559,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7852,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8145,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8513,9 +8438,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8809,9 +8731,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9205,9 +9124,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9501,9 +9417,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9797,9 +9710,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10093,9 +10003,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10389,9 +10296,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10685,9 +10589,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10981,9 +10882,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11277,9 +11175,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11573,9 +11468,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11869,9 +11761,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12165,9 +12054,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12461,9 +12347,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12757,9 +12640,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13153,9 +13033,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13449,9 +13326,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13745,9 +13619,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14041,9 +13912,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -14337,9 +14205,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14633,9 +14498,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -14929,9 +14791,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15225,9 +15084,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -15521,9 +15377,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15817,9 +15670,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16113,9 +15963,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16409,9 +16256,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16705,9 +16549,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -17101,9 +16942,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17397,9 +17235,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -17693,9 +17528,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -17989,9 +17821,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18285,9 +18114,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18581,9 +18407,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -18877,9 +18700,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -19173,9 +18993,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -19469,9 +19286,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -19765,9 +19579,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20061,9 +19872,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -20355,9 +20163,6 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">

--- a/diseases/d059/2005-2009.xlsx
+++ b/diseases/d059/2005-2009.xlsx
@@ -4630,12 +4630,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4674,9 +4674,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -4685,68 +4682,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS28" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4784,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4822,17 +4833,34 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4840,6 +4868,64 @@
           <t>annual</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4857,7 +4943,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -4870,42 +4956,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -4932,17 +5018,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4981,165 +5067,79 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Gulusótt</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN30" t="b">
-        <v>1</v>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5171,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5223,68 +5223,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5311,17 +5325,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -5346,12 +5360,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5360,79 +5374,165 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Gulusótt</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN32" t="b">
+        <v>1</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5594,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5639,12 +5739,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5787,12 +5887,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5932,12 +6032,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6080,12 +6180,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6225,12 +6325,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6373,12 +6473,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6518,12 +6618,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6666,12 +6766,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6811,12 +6911,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6959,12 +7059,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7104,12 +7204,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7252,12 +7352,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7397,12 +7497,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7545,12 +7645,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7690,12 +7790,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7838,12 +7938,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7983,12 +8083,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8131,12 +8231,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8276,12 +8376,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8424,12 +8524,12 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8569,12 +8669,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N54" t="n">
@@ -8687,12 +8787,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -8717,12 +8817,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8739,82 +8839,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8841,17 +8927,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8890,34 +8976,17 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Gulusótt</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -8925,64 +8994,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN56" t="b">
-        <v>1</v>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -9000,7 +9011,7 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -9013,42 +9024,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9075,17 +9086,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9124,76 +9135,165 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -9255,12 +9355,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9373,12 +9473,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9403,12 +9503,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9425,68 +9525,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS59" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9513,17 +9627,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9548,12 +9662,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9562,79 +9676,165 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Gulusótt</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN60" t="b">
+        <v>1</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -9696,12 +9896,12 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9841,12 +10041,12 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9989,12 +10189,12 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -10134,12 +10334,12 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10282,12 +10482,12 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10427,12 +10627,12 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10575,12 +10775,12 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10720,12 +10920,12 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10868,12 +11068,12 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -11013,12 +11213,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11161,12 +11361,12 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11306,12 +11506,12 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11454,12 +11654,12 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11599,12 +11799,12 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11747,12 +11947,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11892,12 +12092,12 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -12040,12 +12240,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12185,12 +12385,12 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12333,12 +12533,12 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12478,12 +12678,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12596,12 +12796,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -12626,12 +12826,12 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12648,82 +12848,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -12750,17 +12936,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -12785,12 +12971,12 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12799,165 +12985,79 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Gulusótt</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD82" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE82" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF82" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG82" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN82" t="b">
-        <v>1</v>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13019,12 +13119,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -13134,12 +13234,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -13164,12 +13264,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13178,9 +13278,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13189,68 +13286,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13277,17 +13388,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -13312,12 +13423,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13326,76 +13437,165 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -13457,12 +13657,12 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13575,12 +13775,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -13605,12 +13805,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13627,68 +13827,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -13715,17 +13929,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -13750,12 +13964,12 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13764,79 +13978,165 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Gulusótt</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE88" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN88" t="b">
+        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -13898,12 +14198,12 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -14043,12 +14343,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N90" t="n">
@@ -14191,12 +14491,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -14336,12 +14636,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N92" t="n">
@@ -14484,12 +14784,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -14629,12 +14929,12 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N94" t="n">
@@ -14777,12 +15077,12 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N95" t="n">
@@ -14922,12 +15222,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N96" t="n">
@@ -15070,12 +15370,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N97" t="n">
@@ -15215,12 +15515,12 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N98" t="n">
@@ -15363,12 +15663,12 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N99" t="n">
@@ -15508,12 +15808,12 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -15656,12 +15956,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N101" t="n">
@@ -15801,12 +16101,12 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N102" t="n">
@@ -15949,12 +16249,12 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N103" t="n">
@@ -16094,12 +16394,12 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N104" t="n">
@@ -16242,12 +16542,12 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N105" t="n">
@@ -16387,12 +16687,12 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N106" t="n">
@@ -16505,12 +16805,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -16535,12 +16835,12 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N107" t="n">
@@ -16557,82 +16857,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -16659,17 +16945,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -16694,12 +16980,12 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N108" t="n">
@@ -16708,165 +16994,79 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Gulusótt</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD108" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE108" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG108" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH108" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN108" t="b">
-        <v>1</v>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -16928,12 +17128,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -17073,12 +17273,12 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N110" t="n">
@@ -17221,12 +17421,12 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N111" t="n">
@@ -17336,12 +17536,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -17366,12 +17566,12 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N112" t="n">
@@ -17380,9 +17580,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17391,68 +17588,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -17479,17 +17690,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -17514,12 +17725,12 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N113" t="n">
@@ -17528,76 +17739,165 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_FR_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:FR:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>France annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_FR_ECDC_YELF_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -17659,12 +17959,12 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N114" t="n">
@@ -17777,12 +18077,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -17807,12 +18107,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N115" t="n">
@@ -17829,68 +18129,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -17917,17 +18231,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -17952,12 +18266,12 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N116" t="n">
@@ -17966,79 +18280,165 @@
       <c r="O116" t="n">
         <v>0</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Gulusótt</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN116" t="b">
+        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_YELLOW_FEVER_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -18100,12 +18500,12 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N117" t="n">
@@ -18245,12 +18645,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -18393,12 +18793,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -18538,12 +18938,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -18686,12 +19086,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -18831,12 +19231,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N122" t="n">
@@ -18979,12 +19379,12 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N123" t="n">
@@ -19124,12 +19524,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N124" t="n">
@@ -19272,12 +19672,12 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N125" t="n">
@@ -19417,12 +19817,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -19565,12 +19965,12 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -19710,12 +20110,12 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N128" t="n">
@@ -19858,12 +20258,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -20003,12 +20403,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -20151,12 +20551,12 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-08-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N131" t="n">
@@ -20233,6 +20633,1178 @@
         </is>
       </c>
       <c r="BC131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>yellow-fever</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D059</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Yellow fever</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>黄热病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -20354,7 +21926,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -20364,7 +21936,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -20384,7 +21956,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -20394,7 +21966,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
